--- a/results/Int Task Remove ACC 0.2/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_1_permute.xlsx
@@ -440,853 +440,853 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7825824070186728</v>
+        <v>0.7562094144697347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7822983328297948</v>
+        <v>0.7625371277902246</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8018264714768326</v>
+        <v>0.7651169451823137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.802195297081177</v>
+        <v>0.7632429972181132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.802195297081177</v>
+        <v>0.7632324032911799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7906145654724303</v>
+        <v>0.7644640453890914</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7906145654724303</v>
+        <v>0.7644640453890914</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7792755323448284</v>
+        <v>0.7623483989437463</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7767361288221515</v>
+        <v>0.7733099743783916</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7767361288221515</v>
+        <v>0.7811957796934039</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7751568489737624</v>
+        <v>0.7855012300726272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7685026857566615</v>
+        <v>0.7757308828664813</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7666075499385945</v>
+        <v>0.7763414069519703</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.767881567744239</v>
+        <v>0.7622954293090798</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7718307482843724</v>
+        <v>0.7638323334497357</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7734100281327615</v>
+        <v>0.7522304139871225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7627356658283078</v>
+        <v>0.753504431792767</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.766462373902842</v>
+        <v>0.753504431792767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7683382837053633</v>
+        <v>0.7622742414552133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7673589340155299</v>
+        <v>0.7575469958369792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.773442987016554</v>
+        <v>0.7625583156440912</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7737058733515654</v>
+        <v>0.7483765787893888</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7573978961245846</v>
+        <v>0.7542103012206558</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7511761220734277</v>
+        <v>0.7537798738930328</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7521236899824612</v>
+        <v>0.7568854639551446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7724039974417629</v>
+        <v>0.7454934611928761</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7736674213204742</v>
+        <v>0.7512106504278769</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7661610355367393</v>
+        <v>0.7515265063975547</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7692136559641847</v>
+        <v>0.7590646739620894</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7753718664537419</v>
+        <v>0.7580343164759106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7644671843304049</v>
+        <v>0.7595288449088333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7610033625908822</v>
+        <v>0.7560862110231772</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7616350745302378</v>
+        <v>0.7438651353864625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7331695852281421</v>
+        <v>0.6544778959676376</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6943232246344114</v>
+        <v>0.6538567779552151</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6978929856432672</v>
+        <v>0.6497459419374331</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6744070343674837</v>
+        <v>0.6397338962501422</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6572468345738691</v>
+        <v>0.6397338962501422</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6411401419586209</v>
+        <v>0.6277352930790268</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6405084300192653</v>
+        <v>0.6453894837618642</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6405084300192653</v>
+        <v>0.6613921989461005</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6497616366440009</v>
+        <v>0.6595500327627</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6469613086246336</v>
+        <v>0.6887994726578592</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6700592082805272</v>
+        <v>0.6372148958460035</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6697539462377826</v>
+        <v>0.6339484350415714</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.65331020979899</v>
+        <v>0.6332935734100281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6548683017935126</v>
+        <v>0.6325771100552061</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6418460113865097</v>
+        <v>0.6192621133707129</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5518262752930005</v>
+        <v>0.6065305674028791</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5365929930982528</v>
+        <v>0.6121947870032134</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5306764810898404</v>
+        <v>0.6124933787956667</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.521285553414972</v>
+        <v>0.5890796231700953</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5178535134562491</v>
+        <v>0.5699077543621476</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5028831175965126</v>
+        <v>0.5699077543621476</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4976936628698556</v>
+        <v>0.5734649596057489</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4958197149056552</v>
+        <v>0.5765175800331943</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4930087929593546</v>
+        <v>0.5774333661614279</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4930087929593546</v>
+        <v>0.5935161243491601</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4958514966864551</v>
+        <v>0.517959452725582</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4974201826079109</v>
+        <v>0.517959452725582</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4942934046919326</v>
+        <v>0.5114536044855471</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4949251166312882</v>
+        <v>0.5142433385779811</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4930193868862879</v>
+        <v>0.5142433385779811</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4955462346437105</v>
+        <v>0.5154749806758926</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4967672828146886</v>
+        <v>0.5154749806758926</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4964514268450108</v>
+        <v>0.5126852465834586</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4974201826079109</v>
+        <v>0.5049053805377791</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4977466325045221</v>
+        <v>0.5049053805377791</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4987047943404888</v>
+        <v>0.4968202524493552</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4977784142853219</v>
+        <v>0.4989570867485669</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4974731522425774</v>
+        <v>0.486901590266143</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4993576941337111</v>
+        <v>0.4840376986851759</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4999788121461334</v>
+        <v>0.4840482926121092</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5003052620427445</v>
+        <v>0.4862169086921209</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.5021580221530783</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4990524320909665</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4990524320909665</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5012316420979115</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4977890082122552</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4968414403032217</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.4990524320909665</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,7 +1306,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,7 +1316,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
